--- a/public/plantillas/comparador-rollos-termicos.xlsx
+++ b/public/plantillas/comparador-rollos-termicos.xlsx
@@ -17,11 +17,12 @@
     <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$9</definedName>
     <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$10</definedName>
     <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$11</definedName>
-    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$14</definedName>
-    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$15</definedName>
-    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$19</definedName>
-    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$20</definedName>
-    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$21</definedName>
+    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$17</definedName>
+    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$18</definedName>
+    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$22</definedName>
+    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$23</definedName>
+    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$24</definedName>
+    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="true"/>
   <extLst>
@@ -696,7 +697,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C57"/>
+  <dimension ref="B1:C66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -762,264 +763,285 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ojo con el «80 × 70» de la caja: son milímetros, no metros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80 mm es el ancho del papel y 70 mm el diámetro del rollo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ninguno de los dos le dice cuántos metros de papel trae.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C17" s="9" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C18" s="10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C22" s="11" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C23" s="12" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calibre del papel (gramos por metro cuadrado)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C28" s="14" t="n">
         <f aca="false">IFERROR(C10*C11,"")</f>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="14" t="n">
-        <f aca="false">IFERROR(C20*C21,"")</f>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
+      <c r="C29" s="14" t="n">
+        <f aca="false">IFERROR(C23*C24,"")</f>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="15" t="n">
-        <f aca="false">IFERROR(C9/C24,"")</f>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
+      <c r="C30" s="15" t="n">
+        <f aca="false">IFERROR(C9/C28,"")</f>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="17" t="n">
-        <f aca="false">IFERROR(C19/C25,"")</f>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="s">
+      <c r="C31" s="17" t="n">
+        <f aca="false">IFERROR(C22/C29,"")</f>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="s">
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="7" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="14" t="n">
-        <f aca="false">IFERROR(ROUNDUP((C14*C24)/C25,0),"")</f>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="7" t="s">
+      <c r="C35" s="14" t="n">
+        <f aca="false">IFERROR(ROUNDUP((C17*C28)/C29,0),"")</f>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="18" t="n">
-        <f aca="false">IFERROR((C31*C25)/((C14*C24)/C15),"")</f>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="7" t="s">
+      <c r="C36" s="18" t="n">
+        <f aca="false">IFERROR((C35*C29)/((C17*C28)/C18),"")</f>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="18" t="n">
-        <f aca="false">IFERROR(C15,"")</f>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7" t="s">
+      <c r="C37" s="18" t="n">
+        <f aca="false">IFERROR(C18,"")</f>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="19" t="n">
-        <f aca="false">IFERROR(C14*C9,"")</f>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16" t="s">
+      <c r="C38" s="19" t="n">
+        <f aca="false">IFERROR(C17*C9,"")</f>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="20" t="n">
-        <f aca="false">IFERROR(C31*C19,"")</f>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="16" t="s">
+      <c r="C39" s="20" t="n">
+        <f aca="false">IFERROR(C35*C22,"")</f>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="20" t="n">
-        <f aca="false">IFERROR(C34-C35,"")</f>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
+      <c r="C40" s="20" t="n">
+        <f aca="false">IFERROR(C38-C39,"")</f>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="7" t="s">
+      <c r="C43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">IFERROR(52/C15,"")</f>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="7" t="s">
+      <c r="C44" s="18" t="n">
+        <f aca="false">IFERROR(52/C18,"")</f>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="14" t="n">
-        <f aca="false">IFERROR(C14*C24*(52/C15),"")</f>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="7" t="s">
+      <c r="C45" s="14" t="n">
+        <f aca="false">IFERROR(C17*C28*(52/C18),"")</f>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="19" t="n">
-        <f aca="false">IFERROR(C14*C9*(52/C15),"")</f>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C43" s="19" t="n">
-        <f aca="false">IFERROR(C31*(52/C15)*C19,"")</f>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="20" t="n">
-        <f aca="false">IFERROR(C42-C43,"")</f>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="19" t="n">
+        <f aca="false">IFERROR(C17*C9*(52/C18),"")</f>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <f aca="false">IFERROR(C35*(52/C18)*C22,"")</f>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="7"/>
+      <c r="B48" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="20" t="n">
+        <f aca="false">IFERROR(C46-C47,"")</f>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="7"/>
+      <c r="B53" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="7" t="s">
-        <v>41</v>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La medida «80 × 70» que traen las cajas son milímetros: 80 mm de</t>
+        </is>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="7" t="s">
-        <v>42</v>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ancho y 70 mm de diámetro del rollo. No dice metros. El calibre en</t>
+        </is>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="7" t="s">
-        <v>43</v>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gramos por metro cuadrado es el grosor, y de ahí sale cuántos metros caben.</t>
+        </is>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1027,11 +1049,42 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B65" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="7" t="s">
         <v>45</v>
       </c>
     </row>

--- a/public/plantillas/comparador-rollos-termicos.xlsx
+++ b/public/plantillas/comparador-rollos-termicos.xlsx
@@ -12,17 +12,16 @@
   </sheets>
   <definedNames>
     <definedName name="COMPARADOR_ENCABEZADO">'Comparacion'!$B$2</definedName>
-    <definedName name="COMPARADOR_AVISO">'Comparacion'!$B$3</definedName>
-    <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$5</definedName>
-    <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$9</definedName>
-    <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$10</definedName>
-    <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$11</definedName>
-    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$17</definedName>
-    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$18</definedName>
-    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$22</definedName>
-    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$23</definedName>
-    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$24</definedName>
-    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$25</definedName>
+    <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$4</definedName>
+    <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$8</definedName>
+    <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$9</definedName>
+    <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$10</definedName>
+    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$16</definedName>
+    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$17</definedName>
+    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$21</definedName>
+    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$22</definedName>
+    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$23</definedName>
+    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$24</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="true"/>
   <extLst>
@@ -697,7 +696,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C66"/>
+  <dimension ref="B1:C65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -714,377 +713,374 @@
     <row r="2" customFormat="false" ht="14" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="14" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="21"/>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
-        <v>4</v>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>45</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ojo con el «80 × 70» de la caja: son milímetros, no metros.</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ojo con el «80 × 70» de la caja: son milímetros, no metros.</t>
+          <t xml:space="preserve">80 mm es el ancho del papel y 70 mm el diámetro del rollo.</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">80 mm es el ancho del papel y 70 mm el diámetro del rollo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
           <t xml:space="preserve">Ninguno de los dos le dice cuántos metros de papel trae.</t>
         </is>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>9</v>
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
-        <v>13</v>
+      <c r="B21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>36</v>
+        <v>6</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Calibre del papel (gramos por metro cuadrado)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C24" s="12" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="6"/>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <f aca="false">IFERROR(C9*C10,"")</f>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="14" t="n">
-        <f aca="false">IFERROR(C10*C11,"")</f>
+        <f aca="false">IFERROR(C22*C23,"")</f>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <f aca="false">IFERROR(C23*C24,"")</f>
+        <v>18</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <f aca="false">IFERROR(C8/C27,"")</f>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <f aca="false">IFERROR(C9/C28,"")</f>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
+      <c r="B30" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="17" t="n">
-        <f aca="false">IFERROR(C22/C29,"")</f>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5" t="s">
+      <c r="C30" s="17" t="n">
+        <f aca="false">IFERROR(C21/C28,"")</f>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4" t="s">
-        <v>21</v>
+      <c r="B34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <f aca="false">IFERROR(ROUNDUP((C16*C27)/C28,0),"")</f>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <f aca="false">IFERROR(ROUNDUP((C17*C28)/C29,0),"")</f>
+        <v>23</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <f aca="false">IFERROR((C34*C28)/((C16*C27)/C17),"")</f>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36" s="18" t="n">
-        <f aca="false">IFERROR((C35*C29)/((C17*C28)/C18),"")</f>
+        <f aca="false">IFERROR(C17,"")</f>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="18" t="n">
-        <f aca="false">IFERROR(C18,"")</f>
+        <v>25</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <f aca="false">IFERROR(C16*C8,"")</f>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="19" t="n">
-        <f aca="false">IFERROR(C17*C9,"")</f>
+      <c r="B38" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <f aca="false">IFERROR(C34*C21,"")</f>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(C35*C22,"")</f>
+        <f aca="false">IFERROR(C37-C38,"")</f>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <f aca="false">IFERROR(C38-C39,"")</f>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="5" t="s">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="6"/>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="18" t="n">
+        <f aca="false">IFERROR(52/C17,"")</f>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="18" t="n">
-        <f aca="false">IFERROR(52/C18,"")</f>
+        <v>31</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <f aca="false">IFERROR(C16*C27*(52/C17),"")</f>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="14" t="n">
-        <f aca="false">IFERROR(C17*C28*(52/C18),"")</f>
+        <v>32</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <f aca="false">IFERROR(C16*C8*(52/C17),"")</f>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C46" s="19" t="n">
-        <f aca="false">IFERROR(C17*C9*(52/C18),"")</f>
+        <f aca="false">IFERROR(C34*(52/C17)*C21,"")</f>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="19" t="n">
-        <f aca="false">IFERROR(C35*(52/C18)*C22,"")</f>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="16" t="s">
+      <c r="B47" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="20" t="n">
-        <f aca="false">IFERROR(C46-C47,"")</f>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="5" t="s">
+      <c r="C47" s="20" t="n">
+        <f aca="false">IFERROR(C45-C46,"")</f>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="7" t="s">
-        <v>38</v>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La medida «80 × 70» que traen las cajas son milímetros: 80 mm de</t>
+        </is>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La medida «80 × 70» que traen las cajas son milímetros: 80 mm de</t>
+          <t xml:space="preserve">ancho y 70 mm de diámetro del rollo. No dice metros. El calibre en</t>
         </is>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ancho y 70 mm de diámetro del rollo. No dice metros. El calibre en</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">gramos por metro cuadrado es el grosor, y de ahí sale cuántos metros caben.</t>
         </is>
       </c>
     </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="7"/>
+    </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="7"/>
+      <c r="B57" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="B59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="7"/>
+      <c r="B60" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="7" t="s">
-        <v>43</v>
-      </c>
+      <c r="B63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="7"/>
+      <c r="B64" s="7" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B66" s="7" t="s">
         <v>45</v>
       </c>
     </row>

--- a/public/plantillas/comparador-rollos-termicos.xlsx
+++ b/public/plantillas/comparador-rollos-termicos.xlsx
@@ -11,17 +11,18 @@
     <sheet name="Comparacion" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comparacion'!$B$1:$D$54</definedName>
     <definedName name="COMPARADOR_ENCABEZADO">'Comparacion'!$B$2</definedName>
     <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$4</definedName>
     <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$8</definedName>
     <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$9</definedName>
     <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$10</definedName>
-    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$16</definedName>
-    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$17</definedName>
-    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$21</definedName>
-    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$22</definedName>
-    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$23</definedName>
-    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$24</definedName>
+    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$13</definedName>
+    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$14</definedName>
+    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$18</definedName>
+    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$19</definedName>
+    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$20</definedName>
+    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="true"/>
   <extLst>
@@ -694,15 +695,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:C65"/>
+  <dimension ref="B1:D54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -723,7 +724,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -761,333 +763,285 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ojo con el «80 × 70» de la caja: son milímetros, no metros.</t>
+          <t xml:space="preserve">Ojo: el «80 × 70» de la caja son milímetros —ancho y diámetro—, y no dice cuántos metros trae.</t>
         </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">80 mm es el ancho del papel y 70 mm el diámetro del rollo.</t>
+          <t xml:space="preserve">¿No lo dice la caja? Le medimos su rollo sin costo y le entregamos la cifra exacta. Solo pídalo.</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ninguno de los dos le dice cuántos metros de papel trae.</t>
-        </is>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>100</v>
-      </c>
+    <row r="15" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="6"/>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
-        <v>13</v>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Calibre del papel (gramos por metro cuadrado)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C21" s="12" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
+    <row r="22" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <f aca="false">IFERROR(C9*C10,"")</f>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <f aca="false">IFERROR(C19*C20,"")</f>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">IFERROR(C8/C24,"")</f>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <f aca="false">IFERROR(C9*C10,"")</f>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <f aca="false">IFERROR(C22*C23,"")</f>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <f aca="false">IFERROR(C8/C27,"")</f>
-      </c>
+      <c r="B27" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <f aca="false">IFERROR(C18/C25,"")</f>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="17" t="n">
-        <f aca="false">IFERROR(C21/C28,"")</f>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="6"/>
+      <c r="B30" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <f aca="false">IFERROR(ROUNDUP((C13*C24)/C25,0),"")</f>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <f aca="false">IFERROR((C31*C25)/((C13*C24)/C14),"")</f>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
-        <v>21</v>
+      <c r="B33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <f aca="false">IFERROR(C14,"")</f>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <f aca="false">IFERROR(ROUNDUP((C16*C27)/C28,0),"")</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">IFERROR(C13*C8,"")</f>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="18" t="n">
-        <f aca="false">IFERROR((C34*C28)/((C16*C27)/C17),"")</f>
+      <c r="B35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <f aca="false">IFERROR(C31*C18,"")</f>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="18" t="n">
-        <f aca="false">IFERROR(C17,"")</f>
+      <c r="B36" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <f aca="false">IFERROR(C34-C35,"")</f>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <f aca="false">IFERROR(C16*C8,"")</f>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <f aca="false">IFERROR(C34*C21,"")</f>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <f aca="false">IFERROR(C37-C38,"")</f>
-      </c>
+      <c r="B37" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="18" t="n">
+        <f aca="false">IFERROR(52/C14,"")</f>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <f aca="false">IFERROR(C13*C24*(52/C14),"")</f>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <f aca="false">IFERROR(C13*C8*(52/C14),"")</f>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="18" t="n">
-        <f aca="false">IFERROR(52/C17,"")</f>
+        <v>33</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <f aca="false">IFERROR(C31*(52/C14)*C18,"")</f>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="14" t="n">
-        <f aca="false">IFERROR(C16*C27*(52/C17),"")</f>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="19" t="n">
-        <f aca="false">IFERROR(C16*C8*(52/C17),"")</f>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="19" t="n">
-        <f aca="false">IFERROR(C34*(52/C17)*C21,"")</f>
-      </c>
+      <c r="B44" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <f aca="false">IFERROR(C42-C43,"")</f>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="20" t="n">
-        <f aca="false">IFERROR(C45-C46,"")</f>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="6"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El rollo se consume por metro, no por caja. El calibre en gramos por metro cuadrado es el grosor:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mientras más grueso el papel, menos metros caben en el mismo diámetro de rollo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metros por caja = rollos × metros por rollo. Costo por metro = precio de la caja ÷ metros que trae.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La medida «80 × 70» que traen las cajas son milímetros: 80 mm de</t>
+          <t xml:space="preserve">Cubre los mismos metros, en el mismo tiempo y con la misma frecuencia. Solo cambia lo que paga.</t>
         </is>
       </c>
+    </row>
+    <row r="53" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ancho y 70 mm de diámetro del rollo. No dice metros. El calibre en</t>
+          <t xml:space="preserve">Todas las celdas amarillas son suyas: llénelas cuando quiera y compruebe usted mismo el resultado.</t>
         </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gramos por metro cuadrado es el grosor, y de ahí sale cuántos metros caben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="7"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="7"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="7"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/public/plantillas/comparador-rollos-termicos.xlsx
+++ b/public/plantillas/comparador-rollos-termicos.xlsx
@@ -11,18 +11,20 @@
     <sheet name="Comparacion" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comparacion'!$B$1:$D$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comparacion'!$B$1:$D$55</definedName>
     <definedName name="COMPARADOR_ENCABEZADO">'Comparacion'!$B$2</definedName>
-    <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$4</definedName>
-    <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$8</definedName>
-    <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$9</definedName>
-    <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$10</definedName>
-    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$13</definedName>
-    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$14</definedName>
-    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$18</definedName>
-    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$19</definedName>
-    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$20</definedName>
-    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$21</definedName>
+    <definedName name="COMPARADOR_EMPRESA">'Comparacion'!$B$3</definedName>
+    <definedName name="COMPARADOR_VENDEDOR">'Comparacion'!$B$4</definedName>
+    <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$6</definedName>
+    <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$10</definedName>
+    <definedName name="CLIENTE_ROLLOS_CAJA">'Comparacion'!$C$11</definedName>
+    <definedName name="CLIENTE_METROS_ROLLO">'Comparacion'!$C$12</definedName>
+    <definedName name="CLIENTE_CAJAS_PEDIDO">'Comparacion'!$C$15</definedName>
+    <definedName name="CLIENTE_SEMANAS">'Comparacion'!$C$16</definedName>
+    <definedName name="NUESTRO_PRECIO_CAJA">'Comparacion'!$C$19</definedName>
+    <definedName name="NUESTRO_ROLLOS_CAJA">'Comparacion'!$C$20</definedName>
+    <definedName name="NUESTRO_METROS_ROLLO">'Comparacion'!$C$21</definedName>
+    <definedName name="NUESTRO_CALIBRE">'Comparacion'!$C$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="true"/>
   <extLst>
@@ -515,6 +517,44 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1325880" cy="454904"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo" descr="Papelería Comercial"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1325880" cy="454904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -697,7 +737,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:D54"/>
+  <dimension ref="B1:D55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -706,7 +746,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -714,325 +754,326 @@
     <row r="2" customFormat="false" ht="14" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+    <row r="3" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="7" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C12" s="10" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ojo: el «80 × 70» de la caja son milímetros —ancho y diámetro—, y no dice cuántos metros trae.</t>
         </is>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="inlineStr">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">¿No lo dice la caja? Le medimos su rollo sin costo y le entregamos la cifra exacta. Solo pídalo.</t>
         </is>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C16" s="10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+    <row r="17" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>36</v>
-      </c>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C21" s="13" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Calibre del papel (gramos por metro cuadrado)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C22" s="12" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
+    <row r="23" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <f aca="false">IFERROR(C9*C10,"")</f>
-      </c>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="14" t="n">
-        <f aca="false">IFERROR(C19*C20,"")</f>
+        <f aca="false">IFERROR(C11*C12,"")</f>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <f aca="false">IFERROR(C20*C21,"")</f>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="15" t="n">
-        <f aca="false">IFERROR(C8/C24,"")</f>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
+      <c r="C27" s="15" t="n">
+        <f aca="false">IFERROR(C10/C25,"")</f>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="17" t="n">
-        <f aca="false">IFERROR(C18/C25,"")</f>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="s">
+      <c r="C28" s="17" t="n">
+        <f aca="false">IFERROR(C19/C26,"")</f>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <f aca="false">IFERROR(ROUNDUP((C13*C24)/C25,0),"")</f>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="18" t="n">
-        <f aca="false">IFERROR((C31*C25)/((C13*C24)/C14),"")</f>
+        <v>22</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <f aca="false">IFERROR(ROUNDUP((C15*C25)/C26,0),"")</f>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="18" t="n">
-        <f aca="false">IFERROR(C14,"")</f>
+        <f aca="false">IFERROR((C32*C26)/((C15*C25)/C16),"")</f>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <f aca="false">IFERROR(C16,"")</f>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="19" t="n">
-        <f aca="false">IFERROR(C13*C8,"")</f>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <f aca="false">IFERROR(C31*C18,"")</f>
+      <c r="C35" s="19" t="n">
+        <f aca="false">IFERROR(C15*C10,"")</f>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <f aca="false">IFERROR(C32*C19,"")</f>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="20" t="n">
-        <f aca="false">IFERROR(C34-C35,"")</f>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
+      <c r="C37" s="20" t="n">
+        <f aca="false">IFERROR(C35-C36,"")</f>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
+    <row r="39" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">IFERROR(52/C14,"")</f>
-      </c>
+      <c r="C40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <f aca="false">IFERROR(C13*C24*(52/C14),"")</f>
+        <v>30</v>
+      </c>
+      <c r="C41" s="18" t="n">
+        <f aca="false">IFERROR(52/C16,"")</f>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C42" s="19" t="n">
-        <f aca="false">IFERROR(C13*C8*(52/C14),"")</f>
+        <v>31</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <f aca="false">IFERROR(C15*C25*(52/C16),"")</f>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <f aca="false">IFERROR(C15*C10*(52/C16),"")</f>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="19" t="n">
-        <f aca="false">IFERROR(C31*(52/C14)*C18,"")</f>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="19" t="n">
+        <f aca="false">IFERROR(C32*(52/C16)*C19,"")</f>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="20" t="n">
-        <f aca="false">IFERROR(C42-C43,"")</f>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="5" t="s">
+      <c r="C45" s="20" t="n">
+        <f aca="false">IFERROR(C43-C44,"")</f>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="C47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">El rollo se consume por metro, no por caja. El calibre en gramos por metro cuadrado es el grosor:</t>
         </is>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="7" t="inlineStr">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">mientras más grueso el papel, menos metros caben en el mismo diámetro de rollo.</t>
         </is>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="7"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="7" t="inlineStr">
+    <row r="50" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Metros por caja = rollos × metros por rollo. Costo por metro = precio de la caja ÷ metros que trae.</t>
         </is>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="7"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="7" t="inlineStr">
+    <row r="52" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cubre los mismos metros, en el mismo tiempo y con la misma frecuencia. Solo cambia lo que paga.</t>
         </is>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="7"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="7" t="inlineStr">
+    <row r="54" customFormat="false" ht="4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Todas las celdas amarillas son suyas: llénelas cuando quiera y compruebe usted mismo el resultado.</t>
         </is>
@@ -1046,5 +1087,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/plantillas/comparador-rollos-termicos.xlsx
+++ b/public/plantillas/comparador-rollos-termicos.xlsx
@@ -12,8 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Comparacion'!$B$1:$D$55</definedName>
-    <definedName name="COMPARADOR_ENCABEZADO">'Comparacion'!$B$2</definedName>
-    <definedName name="COMPARADOR_EMPRESA">'Comparacion'!$B$3</definedName>
+    <definedName name="COMPARADOR_ENCABEZADO">'Comparacion'!$B$3</definedName>
     <definedName name="COMPARADOR_VENDEDOR">'Comparacion'!$B$4</definedName>
     <definedName name="COMPARADOR_NOTA_EJEMPLO">'Comparacion'!$B$6</definedName>
     <definedName name="CLIENTE_PRECIO_CAJA">'Comparacion'!$C$10</definedName>
@@ -523,12 +522,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1325880" cy="454904"/>
+    <xdr:ext cx="1199314" cy="411480"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Logo" descr="Papelería Comercial"/>
@@ -545,7 +544,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1325880" cy="454904"/>
+          <a:ext cx="1199314" cy="411480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -747,14 +746,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
